--- a/output/pdf_financials_xlsx/FF.xlsx
+++ b/output/pdf_financials_xlsx/FF.xlsx
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.059388</v>
+        <v>-0.059388</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.038642</v>
+        <v>-0.038642</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-0.19609</v>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.059388</v>
+        <v>-0.059388</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.038642</v>
+        <v>-0.038642</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-0.19609</v>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.059388</v>
+        <v>-0.059388</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.038642</v>
+        <v>-0.038642</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-0.19609</v>
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.059388</v>
+        <v>-0.059388</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.038642</v>
+        <v>-0.038642</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.19609</v>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.059388</v>
+        <v>-0.059388</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.038642</v>
+        <v>-0.038642</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.19609</v>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -6425,40 +6425,40 @@
         <v>0.246236</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.246236</v>
+        <v>0.275542</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.274416</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>7.717255</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>23.94188</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>27.607</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>30.23</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>47.282</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>49.589</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>53.623</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>57.113</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>62.866</v>
       </c>
     </row>
     <row r="93">
@@ -12092,7 +12092,11 @@
           <t>Warrant and share-based payment reserve (Note 12)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -16421,7 +16425,11 @@
           <t>Warrant and share-based payment reserve (Note 14)</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -23710,7 +23718,11 @@
           <t>Warrant and share‐based payment reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -27003,7 +27015,11 @@
           <t>Warrant and share-based payment reserve (Note 17)</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -29928,7 +29944,11 @@
           <t>Warrant and share-based payment reserve (Note 20)</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -34471,7 +34491,11 @@
           <t>Warrant and share-based payment reserve (Note 13) 7,717,255</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -36097,7 +36121,11 @@
           <t>Share-based payment reserve (Note 12)</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -70391,10 +70419,10 @@
         </is>
       </c>
       <c r="G614" s="5" t="n">
-        <v>0.059388</v>
+        <v>-0.059388</v>
       </c>
       <c r="H614" s="5" t="n">
-        <v>0.038642</v>
+        <v>-0.038642</v>
       </c>
       <c r="I614" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FF.xlsx
+++ b/output/pdf_financials_xlsx/FF.xlsx
@@ -3318,10 +3318,10 @@
         <v>0.103</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>1.009</v>
+        <v>0</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>1.118</v>
+        <v>0</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>0.875</v>
@@ -18201,7 +18201,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>OtherReceivables</t>
+          <t>Receivables</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -19809,7 +19809,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>OtherReceivables</t>
+          <t>Receivables</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -22904,7 +22904,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -24698,7 +24702,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -26302,7 +26310,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -33358,7 +33370,11 @@
           <t>Reclamation deposit (Note 9) 115,215</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FF.xlsx
+++ b/output/pdf_financials_xlsx/FF.xlsx
@@ -564,15 +564,11 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
@@ -646,15 +642,11 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -726,15 +718,11 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
@@ -808,24 +796,20 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>0.003534</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>0.022847</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.052246</v>
@@ -888,15 +872,11 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -968,15 +948,11 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -1048,24 +1024,20 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.022851</v>
+        <v>0.026385</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.034548</v>
+        <v>0.057395</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0.052246</v>
@@ -1128,21 +1100,17 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.022851</v>
+        <v>-0.026385</v>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
@@ -1210,15 +1178,11 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1290,15 +1254,11 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>-0</v>
@@ -1370,15 +1330,11 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>
@@ -1450,15 +1406,11 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0</v>
@@ -1530,15 +1482,11 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.052913</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-0.07739600000000001</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.059388</v>
@@ -1610,15 +1558,11 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1874,15 +1818,11 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.052913</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-0.07739600000000001</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-0.059388</v>
@@ -1954,15 +1894,11 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -2034,15 +1970,11 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
@@ -2114,15 +2046,11 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-0.052913</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>-0.07739600000000001</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-0.059388</v>
@@ -2176,15 +2104,11 @@
           <t>EPS (Basic)</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>-0.01</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>-0.01</v>
@@ -2256,15 +2180,11 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>-0.01</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>-0.01</v>
@@ -2422,15 +2342,11 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.052913</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-0.07739600000000001</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.059388</v>
@@ -2502,15 +2418,11 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
@@ -2582,15 +2494,11 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.052913</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-0.07739600000000001</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.059388</v>
@@ -2754,15 +2662,11 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -3318,10 +3222,10 @@
         <v>0.103</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>0.875</v>
@@ -4934,19 +4838,19 @@
         <v>0</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>2.054</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>2.097</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>2.984</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>2.423</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="68">
@@ -6770,15 +6674,11 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.052913</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-0.07739600000000001</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>-0.059388</v>
@@ -6832,15 +6732,11 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>0</v>
@@ -6894,15 +6790,11 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>0.000968</v>
@@ -6956,15 +6848,11 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D102" s="3" t="n">
         <v>0</v>
@@ -7018,15 +6906,11 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>0</v>
@@ -7080,15 +6964,11 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D104" s="3" t="n">
         <v>0.003193</v>
@@ -7142,15 +7022,11 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>0</v>
@@ -7204,15 +7080,11 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>-0.015162</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>0.007057</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>-0.055227</v>
@@ -7266,15 +7138,11 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>0</v>
@@ -7328,15 +7196,11 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D108" s="3" t="n">
         <v>0</v>
@@ -7390,15 +7254,11 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>0</v>
@@ -7452,15 +7312,11 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -7514,15 +7370,11 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -7576,15 +7428,11 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -7638,15 +7486,11 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>0</v>
@@ -7700,15 +7544,11 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>0</v>
@@ -7729,10 +7569,10 @@
         <v>0</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>0</v>
+        <v>-0.54974</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>0</v>
+        <v>-1.828695</v>
       </c>
       <c r="L114" s="3" t="n">
         <v>0</v>
@@ -7762,15 +7602,11 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -7803,19 +7639,19 @@
         <v>0</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>16.357</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>10.479</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>2.322</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>3.228</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>2.743</v>
       </c>
     </row>
     <row r="116">
@@ -7824,15 +7660,11 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D116" s="3" t="n">
         <v>0</v>
@@ -7886,15 +7718,11 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>0</v>
@@ -7948,15 +7776,11 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>0</v>
@@ -8076,15 +7900,11 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
@@ -8138,15 +7958,11 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>0</v>
@@ -8200,15 +8016,11 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D122" s="3" t="n">
         <v>0</v>
@@ -8262,15 +8074,11 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>0</v>
@@ -8324,15 +8132,11 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -8386,15 +8190,11 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -8448,15 +8248,11 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D126" s="3" t="n">
         <v>0</v>
@@ -8602,15 +8398,11 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D128" s="3" t="n">
         <v>0</v>
@@ -8730,15 +8522,11 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0.242045</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>0.17397</v>
       </c>
       <c r="D130" s="3" t="n">
         <v>0.103631</v>
@@ -8814,15 +8602,11 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>0</v>
@@ -8876,15 +8660,11 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-0.068075</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>-0.070339</v>
       </c>
       <c r="D132" s="3" t="n">
         <v>-0.055227</v>
@@ -8938,15 +8718,11 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.17397</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>0.103631</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>0.048404</v>
@@ -9022,15 +8798,11 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -9153,7 +8925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U615"/>
+  <dimension ref="A1:U625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -40177,7 +39949,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -41175,7 +40951,11 @@
           <t>Proceeds from sale of marketable securities (Note 5)</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -44067,7 +43847,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E352" t="inlineStr">
         <is>
           <t>-</t>
@@ -45653,7 +45437,11 @@
           <t>Proceeds from non-brokered private placement (Note 14 (b))</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E368" t="inlineStr">
         <is>
           <t>-</t>
@@ -47451,7 +47239,11 @@
           <t>Proceeds from sale of investments (Note 4)</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr">
         <is>
           <t>-</t>
@@ -50338,7 +50130,11 @@
           <t>Proceeds from sale of investments (Note 5)</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
           <t>-</t>
@@ -55673,7 +55469,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D468" t="inlineStr"/>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E468" t="inlineStr">
         <is>
           <t>-</t>
@@ -55976,7 +55776,11 @@
           <t>Issuance of shares for cash in private placement (Note 17)</t>
         </is>
       </c>
-      <c r="D471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E471" t="inlineStr">
         <is>
           <t>-</t>
@@ -58798,7 +58602,11 @@
           <t>Issuance of shares for cash in private placement (Note 20(b))</t>
         </is>
       </c>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr">
         <is>
           <t>-</t>
@@ -64131,7 +63939,11 @@
           <t>Shares issued for private placement</t>
         </is>
       </c>
-      <c r="D552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E552" t="inlineStr">
         <is>
           <t>-</t>
@@ -64750,15 +64562,11 @@
           <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
-      <c r="E558" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F558" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E558" s="5" t="n">
+        <v>-0.052913</v>
+      </c>
+      <c r="F558" s="5" t="n">
+        <v>-0.07739600000000001</v>
       </c>
       <c r="G558" s="5" t="n">
         <v>-0.059388</v>
@@ -65453,29 +65261,29 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Non-cash item</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Administrative and office $</t>
-        </is>
-      </c>
-      <c r="D565" t="inlineStr"/>
-      <c r="E565" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F565" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Change in non-cash working capital</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E565" s="5" t="n">
+        <v>-0.015162</v>
+      </c>
+      <c r="F565" s="5" t="n">
+        <v>0.007057</v>
       </c>
       <c r="G565" t="inlineStr">
         <is>
@@ -65492,14 +65300,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J565" s="5" t="n">
-        <v>0.028374</v>
-      </c>
-      <c r="K565" s="5" t="n">
-        <v>0.048315</v>
-      </c>
-      <c r="L565" s="5" t="n">
-        <v>0.17597</v>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M565" t="inlineStr">
         <is>
@@ -65550,33 +65364,25 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Non-cash item</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D566" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E566" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F566" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Non-cash item total</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr"/>
+      <c r="E566" s="5" t="n">
+        <v>-0.068075</v>
+      </c>
+      <c r="F566" s="5" t="n">
+        <v>-0.070339</v>
       </c>
       <c r="G566" t="inlineStr">
         <is>
@@ -65598,11 +65404,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K566" s="5" t="n">
-        <v>0.008793</v>
-      </c>
-      <c r="L566" s="5" t="n">
-        <v>0.00691</v>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M566" t="inlineStr">
         <is>
@@ -65653,29 +65463,29 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Non-cash item</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Exploration and evaluation</t>
-        </is>
-      </c>
-      <c r="D567" t="inlineStr"/>
-      <c r="E567" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F567" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Change in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E567" s="5" t="n">
+        <v>-0.068075</v>
+      </c>
+      <c r="F567" s="5" t="n">
+        <v>-0.070339</v>
       </c>
       <c r="G567" t="inlineStr">
         <is>
@@ -65697,11 +65507,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K567" s="5" t="n">
-        <v>0.107916</v>
-      </c>
-      <c r="L567" s="5" t="n">
-        <v>0.08622100000000001</v>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M567" t="inlineStr">
         <is>
@@ -65752,29 +65566,29 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Non-cash item</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Investor relations and marketing</t>
-        </is>
-      </c>
-      <c r="D568" t="inlineStr"/>
-      <c r="E568" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F568" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash and cash equivalents, beginning of year</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E568" s="5" t="n">
+        <v>0.242045</v>
+      </c>
+      <c r="F568" s="5" t="n">
+        <v>0.17397</v>
       </c>
       <c r="G568" t="inlineStr">
         <is>
@@ -65801,8 +65615,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L568" s="5" t="n">
-        <v>0.568813</v>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M568" t="inlineStr">
         <is>
@@ -65853,33 +65669,29 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Non-cash item</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Cash, end of year $</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E569" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F569" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E569" s="5" t="n">
+        <v>0.17397</v>
+      </c>
+      <c r="F569" s="5" t="n">
+        <v>0.103631</v>
       </c>
       <c r="G569" t="inlineStr">
         <is>
@@ -65896,14 +65708,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J569" s="5" t="n">
-        <v>0.167814</v>
-      </c>
-      <c r="K569" s="5" t="n">
-        <v>0.232711</v>
-      </c>
-      <c r="L569" s="5" t="n">
-        <v>0.476427</v>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M569" t="inlineStr">
         <is>
@@ -65964,7 +65782,7 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Salaries and consultants</t>
+          <t>Administrative and office $</t>
         </is>
       </c>
       <c r="D570" t="inlineStr"/>
@@ -65994,13 +65812,13 @@
         </is>
       </c>
       <c r="J570" s="5" t="n">
-        <v>0.182219</v>
+        <v>0.028374</v>
       </c>
       <c r="K570" s="5" t="n">
-        <v>0.162148</v>
+        <v>0.048315</v>
       </c>
       <c r="L570" s="5" t="n">
-        <v>0.618892</v>
+        <v>0.17597</v>
       </c>
       <c r="M570" t="inlineStr">
         <is>
@@ -66061,10 +65879,14 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Share-based payments (Note 13(c))</t>
-        </is>
-      </c>
-      <c r="D571" t="inlineStr"/>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E571" t="inlineStr">
         <is>
           <t>-</t>
@@ -66095,13 +65917,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K571" s="5" t="n">
+        <v>0.008793</v>
       </c>
       <c r="L571" s="5" t="n">
-        <v>1.267851</v>
+        <v>0.00691</v>
       </c>
       <c r="M571" t="inlineStr">
         <is>
@@ -66162,14 +65982,10 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
-        </is>
-      </c>
-      <c r="D572" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr"/>
       <c r="E572" t="inlineStr">
         <is>
           <t>-</t>
@@ -66195,14 +66011,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J572" s="5" t="n">
-        <v>0.005695</v>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K572" s="5" t="n">
-        <v>0.004513</v>
+        <v>0.107916</v>
       </c>
       <c r="L572" s="5" t="n">
-        <v>0.1074</v>
+        <v>0.08622100000000001</v>
       </c>
       <c r="M572" t="inlineStr">
         <is>
@@ -66263,7 +66081,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Travel and accommodation</t>
+          <t>Investor relations and marketing</t>
         </is>
       </c>
       <c r="D573" t="inlineStr"/>
@@ -66297,11 +66115,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K573" s="5" t="n">
-        <v>0.014664</v>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L573" s="5" t="n">
-        <v>0.178115</v>
+        <v>0.568813</v>
       </c>
       <c r="M573" t="inlineStr">
         <is>
@@ -66362,12 +66182,12 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Loss before other items</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
@@ -66395,16 +66215,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J574" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J574" s="5" t="n">
+        <v>0.167814</v>
       </c>
       <c r="K574" s="5" t="n">
-        <v>-0.57906</v>
+        <v>0.232711</v>
       </c>
       <c r="L574" s="5" t="n">
-        <v>-3.486599</v>
+        <v>0.476427</v>
       </c>
       <c r="M574" t="inlineStr">
         <is>
@@ -66465,7 +66283,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Charge related to public company listing (Note 4)</t>
+          <t>Salaries and consultants</t>
         </is>
       </c>
       <c r="D575" t="inlineStr"/>
@@ -66494,18 +66312,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J575" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K575" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J575" s="5" t="n">
+        <v>0.182219</v>
+      </c>
+      <c r="K575" s="5" t="n">
+        <v>0.162148</v>
       </c>
       <c r="L575" s="5" t="n">
-        <v>-0.65513</v>
+        <v>0.618892</v>
       </c>
       <c r="M575" t="inlineStr">
         <is>
@@ -66566,14 +66380,10 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Foreign exchange (loss) gain</t>
-        </is>
-      </c>
-      <c r="D576" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Share-based payments (Note 13(c))</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr"/>
       <c r="E576" t="inlineStr">
         <is>
           <t>-</t>
@@ -66604,11 +66414,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K576" s="5" t="n">
-        <v>0.041153</v>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L576" s="5" t="n">
-        <v>-0.271659</v>
+        <v>1.267851</v>
       </c>
       <c r="M576" t="inlineStr">
         <is>
@@ -66669,10 +66481,14 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Gain on debt settlement (Note 13 (b))</t>
-        </is>
-      </c>
-      <c r="D577" t="inlineStr"/>
+          <t>Transfer agent and filing fees</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E577" t="inlineStr">
         <is>
           <t>-</t>
@@ -66698,18 +66514,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J577" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K577" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J577" s="5" t="n">
+        <v>0.005695</v>
+      </c>
+      <c r="K577" s="5" t="n">
+        <v>0.004513</v>
       </c>
       <c r="L577" s="5" t="n">
-        <v>0.09976400000000001</v>
+        <v>0.1074</v>
       </c>
       <c r="M577" t="inlineStr">
         <is>
@@ -66770,7 +66582,7 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Gain on fair value adjustment of derivative liability</t>
+          <t>Travel and accommodation</t>
         </is>
       </c>
       <c r="D578" t="inlineStr"/>
@@ -66805,12 +66617,10 @@
         </is>
       </c>
       <c r="K578" s="5" t="n">
-        <v>0.104821</v>
-      </c>
-      <c r="L578" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.014664</v>
+      </c>
+      <c r="L578" s="5" t="n">
+        <v>0.178115</v>
       </c>
       <c r="M578" t="inlineStr">
         <is>
@@ -66871,10 +66681,14 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Interest and other expenses</t>
-        </is>
-      </c>
-      <c r="D579" t="inlineStr"/>
+          <t>Loss before other items</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E579" t="inlineStr">
         <is>
           <t>-</t>
@@ -66906,10 +66720,10 @@
         </is>
       </c>
       <c r="K579" s="5" t="n">
-        <v>-0.047992</v>
+        <v>-0.57906</v>
       </c>
       <c r="L579" s="5" t="n">
-        <v>-0.209044</v>
+        <v>-3.486599</v>
       </c>
       <c r="M579" t="inlineStr">
         <is>
@@ -66970,14 +66784,10 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Interest and other income</t>
-        </is>
-      </c>
-      <c r="D580" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Charge related to public company listing (Note 4)</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr"/>
       <c r="E580" t="inlineStr">
         <is>
           <t>-</t>
@@ -67014,7 +66824,7 @@
         </is>
       </c>
       <c r="L580" s="5" t="n">
-        <v>0.007155</v>
+        <v>-0.65513</v>
       </c>
       <c r="M580" t="inlineStr">
         <is>
@@ -67075,10 +66885,14 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Write-down of mineral properties (Note 9)</t>
-        </is>
-      </c>
-      <c r="D581" t="inlineStr"/>
+          <t>Foreign exchange (loss) gain</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E581" t="inlineStr">
         <is>
           <t>-</t>
@@ -67110,10 +66924,10 @@
         </is>
       </c>
       <c r="K581" s="5" t="n">
-        <v>-0.24206</v>
+        <v>0.041153</v>
       </c>
       <c r="L581" s="5" t="n">
-        <v>-0.566544</v>
+        <v>-0.271659</v>
       </c>
       <c r="M581" t="inlineStr">
         <is>
@@ -67174,14 +66988,10 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
-        </is>
-      </c>
-      <c r="D582" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Gain on debt settlement (Note 13 (b))</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr"/>
       <c r="E582" t="inlineStr">
         <is>
           <t>-</t>
@@ -67212,11 +67022,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K582" s="5" t="n">
-        <v>-0.7231379999999999</v>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L582" s="5" t="n">
-        <v>-5.082057</v>
+        <v>0.09976400000000001</v>
       </c>
       <c r="M582" t="inlineStr">
         <is>
@@ -67272,12 +67084,12 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Other comprehensive income for the year</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Currency translation adjustment</t>
+          <t>Gain on fair value adjustment of derivative liability</t>
         </is>
       </c>
       <c r="D583" t="inlineStr"/>
@@ -67312,10 +67124,12 @@
         </is>
       </c>
       <c r="K583" s="5" t="n">
-        <v>0.417314</v>
-      </c>
-      <c r="L583" s="5" t="n">
-        <v>1.424729</v>
+        <v>0.104821</v>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M583" t="inlineStr">
         <is>
@@ -67371,19 +67185,15 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Other comprehensive income for the year</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D584" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Interest and other expenses</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr"/>
       <c r="E584" t="inlineStr">
         <is>
           <t>-</t>
@@ -67415,10 +67225,10 @@
         </is>
       </c>
       <c r="K584" s="5" t="n">
-        <v>-0.305824</v>
+        <v>-0.047992</v>
       </c>
       <c r="L584" s="5" t="n">
-        <v>-3.657328</v>
+        <v>-0.209044</v>
       </c>
       <c r="M584" t="inlineStr">
         <is>
@@ -67474,17 +67284,17 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Other comprehensive income for the year</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
+          <t>Interest and other income</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
@@ -67517,11 +67327,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K585" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L585" s="5" t="n">
-        <v>-5e-08</v>
+        <v>0.007155</v>
       </c>
       <c r="M585" t="inlineStr">
         <is>
@@ -67577,12 +67389,12 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Other comprehensive income for the year</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding – Basic and Diluted</t>
+          <t>Write-down of mineral properties (Note 9)</t>
         </is>
       </c>
       <c r="D586" t="inlineStr"/>
@@ -67617,10 +67429,10 @@
         </is>
       </c>
       <c r="K586" s="5" t="n">
-        <v>36.268709</v>
+        <v>-0.24206</v>
       </c>
       <c r="L586" s="5" t="n">
-        <v>105.473169</v>
+        <v>-0.566544</v>
       </c>
       <c r="M586" t="inlineStr">
         <is>
@@ -67681,12 +67493,12 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Depreciation (Note 6)</t>
+          <t>Net loss for the year $</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
@@ -67714,16 +67526,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J587" s="5" t="n">
-        <v>0.020404</v>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K587" s="5" t="n">
-        <v>0.00796</v>
-      </c>
-      <c r="L587" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.7231379999999999</v>
+      </c>
+      <c r="L587" s="5" t="n">
+        <v>-5.082057</v>
       </c>
       <c r="M587" t="inlineStr">
         <is>
@@ -67779,19 +67591,15 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Other comprehensive income for the year</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Investor relations</t>
-        </is>
-      </c>
-      <c r="D588" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Currency translation adjustment</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr"/>
       <c r="E588" t="inlineStr">
         <is>
           <t>-</t>
@@ -67817,18 +67625,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J588" s="5" t="n">
-        <v>0.005647</v>
-      </c>
-      <c r="K588" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L588" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K588" s="5" t="n">
+        <v>0.417314</v>
+      </c>
+      <c r="L588" s="5" t="n">
+        <v>1.424729</v>
       </c>
       <c r="M588" t="inlineStr">
         <is>
@@ -67884,15 +67690,19 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Other comprehensive income for the year</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Reconnaissance expense and sundry exploration</t>
-        </is>
-      </c>
-      <c r="D589" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E589" t="inlineStr">
         <is>
           <t>-</t>
@@ -67918,16 +67728,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J589" s="5" t="n">
-        <v>0.184326</v>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K589" s="5" t="n">
-        <v>0.09769700000000001</v>
-      </c>
-      <c r="L589" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.305824</v>
+      </c>
+      <c r="L589" s="5" t="n">
+        <v>-3.657328</v>
       </c>
       <c r="M589" t="inlineStr">
         <is>
@@ -67983,17 +67793,17 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Other comprehensive income for the year</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Basic and diluted loss per share $</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
@@ -68021,16 +67831,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J590" s="5" t="n">
-        <v>0.040904</v>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K590" s="5" t="n">
-        <v>0.013275</v>
-      </c>
-      <c r="L590" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2e-08</v>
+      </c>
+      <c r="L590" s="5" t="n">
+        <v>-5e-08</v>
       </c>
       <c r="M590" t="inlineStr">
         <is>
@@ -68086,19 +67896,15 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Other comprehensive income for the year</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Total general and administrative expenses</t>
-        </is>
-      </c>
-      <c r="D591" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Weighted average number of shares outstanding – Basic and Diluted</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr"/>
       <c r="E591" t="inlineStr">
         <is>
           <t>-</t>
@@ -68124,16 +67930,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J591" s="5" t="n">
-        <v>-0.635383</v>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K591" s="5" t="n">
-        <v>-0.524223</v>
-      </c>
-      <c r="L591" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>36.268709</v>
+      </c>
+      <c r="L591" s="5" t="n">
+        <v>105.473169</v>
       </c>
       <c r="M591" t="inlineStr">
         <is>
@@ -68194,10 +68000,14 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Write-down of mineral properties (Note 7)</t>
-        </is>
-      </c>
-      <c r="D592" t="inlineStr"/>
+          <t>Depreciation (Note 6)</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E592" t="inlineStr">
         <is>
           <t>-</t>
@@ -68223,13 +68033,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J592" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J592" s="5" t="n">
+        <v>0.020404</v>
       </c>
       <c r="K592" s="5" t="n">
-        <v>-0.221221</v>
+        <v>0.00796</v>
       </c>
       <c r="L592" t="inlineStr">
         <is>
@@ -68295,10 +68103,14 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Gain on fair value adjustment of derivative liability (Note 11)</t>
-        </is>
-      </c>
-      <c r="D593" t="inlineStr"/>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E593" t="inlineStr">
         <is>
           <t>-</t>
@@ -68325,10 +68137,12 @@
         </is>
       </c>
       <c r="J593" s="5" t="n">
-        <v>0.168672</v>
-      </c>
-      <c r="K593" s="5" t="n">
-        <v>0.09489499999999999</v>
+        <v>0.005647</v>
+      </c>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L593" t="inlineStr">
         <is>
@@ -68394,14 +68208,10 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
-        </is>
-      </c>
-      <c r="D594" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Reconnaissance expense and sundry exploration</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr"/>
       <c r="E594" t="inlineStr">
         <is>
           <t>-</t>
@@ -68428,10 +68238,10 @@
         </is>
       </c>
       <c r="J594" s="5" t="n">
-        <v>0.024404</v>
+        <v>0.184326</v>
       </c>
       <c r="K594" s="5" t="n">
-        <v>0.039339</v>
+        <v>0.09769700000000001</v>
       </c>
       <c r="L594" t="inlineStr">
         <is>
@@ -68497,10 +68307,14 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Financing costs and other</t>
-        </is>
-      </c>
-      <c r="D595" t="inlineStr"/>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E595" t="inlineStr">
         <is>
           <t>-</t>
@@ -68527,10 +68341,10 @@
         </is>
       </c>
       <c r="J595" s="5" t="n">
-        <v>-0.00391</v>
+        <v>0.040904</v>
       </c>
       <c r="K595" s="5" t="n">
-        <v>-0.043447</v>
+        <v>0.013275</v>
       </c>
       <c r="L595" t="inlineStr">
         <is>
@@ -68596,10 +68410,14 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Option recoveries (Note 7)</t>
-        </is>
-      </c>
-      <c r="D596" t="inlineStr"/>
+          <t>Total general and administrative expenses</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E596" t="inlineStr">
         <is>
           <t>-</t>
@@ -68626,12 +68444,10 @@
         </is>
       </c>
       <c r="J596" s="5" t="n">
-        <v>0.06654400000000001</v>
-      </c>
-      <c r="K596" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.635383</v>
+      </c>
+      <c r="K596" s="5" t="n">
+        <v>-0.524223</v>
       </c>
       <c r="L596" t="inlineStr">
         <is>
@@ -68697,14 +68513,10 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D597" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Write-down of mineral properties (Note 7)</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr"/>
       <c r="E597" t="inlineStr">
         <is>
           <t>-</t>
@@ -68730,11 +68542,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J597" s="5" t="n">
-        <v>-0.379673</v>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K597" s="5" t="n">
-        <v>-0.654657</v>
+        <v>-0.221221</v>
       </c>
       <c r="L597" t="inlineStr">
         <is>
@@ -68800,14 +68614,10 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
-        </is>
-      </c>
-      <c r="D598" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Gain on fair value adjustment of derivative liability (Note 11)</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr"/>
       <c r="E598" t="inlineStr">
         <is>
           <t>-</t>
@@ -68834,10 +68644,10 @@
         </is>
       </c>
       <c r="J598" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.168672</v>
       </c>
       <c r="K598" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.09489499999999999</v>
       </c>
       <c r="L598" t="inlineStr">
         <is>
@@ -68903,12 +68713,12 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Foreign exchange gain</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
@@ -68937,10 +68747,10 @@
         </is>
       </c>
       <c r="J599" s="5" t="n">
-        <v>26.59698</v>
+        <v>0.024404</v>
       </c>
       <c r="K599" s="5" t="n">
-        <v>36.268709</v>
+        <v>0.039339</v>
       </c>
       <c r="L599" t="inlineStr">
         <is>
@@ -69001,19 +68811,15 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>General and administrative (Note 8) $</t>
-        </is>
-      </c>
-      <c r="D600" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Financing costs and other</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr">
         <is>
           <t>-</t>
@@ -69034,16 +68840,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I600" s="5" t="n">
-        <v>0.19609</v>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J600" s="5" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="K600" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.00391</v>
+      </c>
+      <c r="K600" s="5" t="n">
+        <v>-0.043447</v>
       </c>
       <c r="L600" t="inlineStr">
         <is>
@@ -69104,12 +68910,12 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Comprehensive loss $</t>
+          <t>Option recoveries (Note 7)</t>
         </is>
       </c>
       <c r="D601" t="inlineStr"/>
@@ -69128,14 +68934,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H601" s="5" t="n">
-        <v>0.038642</v>
-      </c>
-      <c r="I601" s="5" t="n">
-        <v>0.19609</v>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J601" s="5" t="n">
-        <v>0.076</v>
+        <v>0.06654400000000001</v>
       </c>
       <c r="K601" t="inlineStr">
         <is>
@@ -69201,17 +69011,17 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
+          <t>Comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
@@ -69229,19 +69039,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H602" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="I602" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J602" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="K602" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.379673</v>
+      </c>
+      <c r="K602" s="5" t="n">
+        <v>-0.654657</v>
       </c>
       <c r="L602" t="inlineStr">
         <is>
@@ -69302,15 +69114,19 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Weighted average number of shares</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding (basic and diluted)</t>
-        </is>
-      </c>
-      <c r="D603" t="inlineStr"/>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E603" t="inlineStr">
         <is>
           <t>-</t>
@@ -69326,19 +69142,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H603" s="5" t="n">
-        <v>6.0075</v>
-      </c>
-      <c r="I603" s="5" t="n">
-        <v>9.519712999999999</v>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J603" s="5" t="n">
-        <v>10.7685</v>
-      </c>
-      <c r="K603" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-08</v>
+      </c>
+      <c r="K603" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="L603" t="inlineStr">
         <is>
@@ -69399,17 +69217,17 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Legal $</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>SharesOutstanding</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
@@ -69427,21 +69245,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H604" s="5" t="n">
-        <v>0.012265</v>
-      </c>
-      <c r="I604" s="5" t="n">
-        <v>0.019496</v>
-      </c>
-      <c r="J604" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K604" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J604" s="5" t="n">
+        <v>26.59698</v>
+      </c>
+      <c r="K604" s="5" t="n">
+        <v>36.268709</v>
       </c>
       <c r="L604" t="inlineStr">
         <is>
@@ -69507,10 +69325,14 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Accounting , audit and tax</t>
-        </is>
-      </c>
-      <c r="D605" t="inlineStr"/>
+          <t>General and administrative (Note 8) $</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E605" t="inlineStr">
         <is>
           <t>-</t>
@@ -69526,16 +69348,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H605" s="5" t="n">
-        <v>0.009925</v>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I605" s="5" t="n">
-        <v>0.00886</v>
-      </c>
-      <c r="J605" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.19609</v>
+      </c>
+      <c r="J605" s="5" t="n">
+        <v>0.076</v>
       </c>
       <c r="K605" t="inlineStr">
         <is>
@@ -69606,7 +69428,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Meals and entertainment</t>
+          <t>Comprehensive loss $</t>
         </is>
       </c>
       <c r="D606" t="inlineStr"/>
@@ -69625,18 +69447,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H606" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H606" s="5" t="n">
+        <v>0.038642</v>
       </c>
       <c r="I606" s="5" t="n">
-        <v>0.001992</v>
-      </c>
-      <c r="J606" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.19609</v>
+      </c>
+      <c r="J606" s="5" t="n">
+        <v>0.076</v>
       </c>
       <c r="K606" t="inlineStr">
         <is>
@@ -69707,12 +69525,12 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Listing and transfer agent</t>
+          <t>Basic and diluted loss per share $</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
@@ -69731,15 +69549,13 @@
         </is>
       </c>
       <c r="H607" s="5" t="n">
-        <v>0.010586</v>
+        <v>-1e-08</v>
       </c>
       <c r="I607" s="5" t="n">
-        <v>0.015052</v>
-      </c>
-      <c r="J607" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2e-08</v>
+      </c>
+      <c r="J607" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="K607" t="inlineStr">
         <is>
@@ -69805,12 +69621,12 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of shares</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>New releases</t>
+          <t>Weighted average number of shares outstanding (basic and diluted)</t>
         </is>
       </c>
       <c r="D608" t="inlineStr"/>
@@ -69829,18 +69645,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H608" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H608" s="5" t="n">
+        <v>6.0075</v>
       </c>
       <c r="I608" s="5" t="n">
-        <v>0.000767</v>
-      </c>
-      <c r="J608" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9.519712999999999</v>
+      </c>
+      <c r="J608" s="5" t="n">
+        <v>10.7685</v>
       </c>
       <c r="K608" t="inlineStr">
         <is>
@@ -69911,10 +69723,14 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Office expenses</t>
-        </is>
-      </c>
-      <c r="D609" t="inlineStr"/>
+          <t>Legal $</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E609" t="inlineStr">
         <is>
           <t>-</t>
@@ -69931,10 +69747,10 @@
         </is>
       </c>
       <c r="H609" s="5" t="n">
-        <v>0.003534</v>
+        <v>0.012265</v>
       </c>
       <c r="I609" s="5" t="n">
-        <v>0.022847</v>
+        <v>0.019496</v>
       </c>
       <c r="J609" t="inlineStr">
         <is>
@@ -70010,7 +69826,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Travel expenses</t>
+          <t>Accounting , audit and tax</t>
         </is>
       </c>
       <c r="D610" t="inlineStr"/>
@@ -70029,13 +69845,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H610" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H610" s="5" t="n">
+        <v>0.009925</v>
       </c>
       <c r="I610" s="5" t="n">
-        <v>0.029384</v>
+        <v>0.00886</v>
       </c>
       <c r="J610" t="inlineStr">
         <is>
@@ -70111,7 +69925,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Project evaluation</t>
+          <t>Meals and entertainment</t>
         </is>
       </c>
       <c r="D611" t="inlineStr"/>
@@ -70130,13 +69944,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H611" s="5" t="n">
-        <v>0.000532</v>
-      </c>
-      <c r="I611" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I611" s="5" t="n">
+        <v>0.001992</v>
       </c>
       <c r="J611" t="inlineStr">
         <is>
@@ -70212,10 +70026,14 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Share-based payments</t>
-        </is>
-      </c>
-      <c r="D612" t="inlineStr"/>
+          <t>Listing and transfer agent</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E612" t="inlineStr">
         <is>
           <t>-</t>
@@ -70231,13 +70049,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H612" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H612" s="5" t="n">
+        <v>0.010586</v>
       </c>
       <c r="I612" s="5" t="n">
-        <v>0.097692</v>
+        <v>0.015052</v>
       </c>
       <c r="J612" t="inlineStr">
         <is>
@@ -70313,14 +70129,10 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>General and administrative (note 8) $</t>
-        </is>
-      </c>
-      <c r="D613" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>New releases</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr">
         <is>
           <t>-</t>
@@ -70331,16 +70143,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G613" s="5" t="n">
-        <v>0.059388</v>
-      </c>
-      <c r="H613" s="5" t="n">
-        <v>0.038642</v>
-      </c>
-      <c r="I613" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I613" s="5" t="n">
+        <v>0.000767</v>
       </c>
       <c r="J613" t="inlineStr">
         <is>
@@ -70416,12 +70230,12 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
+          <t>Office expenses</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
@@ -70434,16 +70248,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G614" s="5" t="n">
-        <v>-0.059388</v>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H614" s="5" t="n">
-        <v>-0.038642</v>
-      </c>
-      <c r="I614" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.003534</v>
+      </c>
+      <c r="I614" s="5" t="n">
+        <v>0.022847</v>
       </c>
       <c r="J614" t="inlineStr">
         <is>
@@ -70514,96 +70328,1112 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Travel expenses</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr"/>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I615" s="5" t="n">
+        <v>0.029384</v>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Project evaluation</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr"/>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H616" s="5" t="n">
+        <v>0.000532</v>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Share-based payments</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr"/>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I617" s="5" t="n">
+        <v>0.097692</v>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>General and administrative (note 8) $</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G618" s="5" t="n">
+        <v>0.059388</v>
+      </c>
+      <c r="H618" s="5" t="n">
+        <v>0.038642</v>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G619" s="5" t="n">
+        <v>-0.059388</v>
+      </c>
+      <c r="H619" s="5" t="n">
+        <v>-0.038642</v>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
           <t>Loss per share</t>
         </is>
       </c>
-      <c r="C615" t="inlineStr">
+      <c r="C620" t="inlineStr">
         <is>
           <t>Basic and diluted (note 6) $</t>
         </is>
       </c>
-      <c r="D615" t="inlineStr">
+      <c r="D620" t="inlineStr">
         <is>
           <t>BasicEPS</t>
         </is>
       </c>
-      <c r="E615" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F615" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G615" s="5" t="n">
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G620" s="5" t="n">
         <v>-1e-08</v>
       </c>
-      <c r="H615" s="5" t="n">
+      <c r="H620" s="5" t="n">
         <v>-1e-08</v>
       </c>
-      <c r="I615" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J615" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K615" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L615" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M615" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N615" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O615" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P615" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q615" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R615" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S615" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T615" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U615" t="inlineStr">
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Expenses and other income</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>General and administrative $</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E621" s="5" t="n">
+        <v>0.052913</v>
+      </c>
+      <c r="F621" s="5" t="n">
+        <v>0.07739600000000001</v>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Expenses and other income</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E622" s="5" t="n">
+        <v>-0.052913</v>
+      </c>
+      <c r="F622" s="5" t="n">
+        <v>-0.07739600000000001</v>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Expenses and other income</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Deficit, beginning of year</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr"/>
+      <c r="E623" s="5" t="n">
+        <v>0.330316</v>
+      </c>
+      <c r="F623" s="5" t="n">
+        <v>0.383229</v>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Expenses and other income</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Deficit, end of year $</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr"/>
+      <c r="E624" s="5" t="n">
+        <v>0.383229</v>
+      </c>
+      <c r="F624" s="5" t="n">
+        <v>0.460625</v>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Loss per share</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Basic and diluted (note 4) $</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E625" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="F625" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U625" t="inlineStr">
         <is>
           <t>-</t>
         </is>
